--- a/sample_data/sample_product_master.xlsx
+++ b/sample_data/sample_product_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MED-LENS-001</t>
+          <t>VIS-SLIT-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optical Lens Kit</t>
+          <t>Slit Lamp Examination Unit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Medical Device</t>
+          <t>Vision Systems</t>
         </is>
       </c>
       <c r="D2" t="b">
@@ -461,17 +461,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MED-GLOVE-002</t>
+          <t>VIS-LENS-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nitrile Exam Gloves (Box of 100)</t>
+          <t>Trial Lens Set (Standard)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Medical Device</t>
+          <t>Vision Systems</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -481,17 +481,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MED-MASK-003</t>
+          <t>VIS-REFR-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Surgical Face Mask (Box of 50)</t>
+          <t>Digital Refractor Head</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Medical Device</t>
+          <t>Vision Systems</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -501,37 +501,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IND-VALVE-004</t>
+          <t>VIS-LOUPE-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Industrial Pressure Valve</t>
+          <t>Surgical Loupe Set (Legacy)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Industrial Equipment</t>
+          <t>Vision Systems</t>
         </is>
       </c>
       <c r="D5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IND-PUMP-005</t>
+          <t>DIAG-OCT-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hydraulic Pump Unit</t>
+          <t>Handheld OCT Scanner</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrial Equipment</t>
+          <t>Diagnostic Equipment</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -541,17 +541,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OFF-CHAIR-006</t>
+          <t>DIAG-FUND-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ergonomic Office Chair</t>
+          <t>Fundus Camera Unit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Office Furniture</t>
+          <t>Diagnostic Equipment</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -561,17 +561,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OFF-DESK-007</t>
+          <t>DIAG-TONO-007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Adjustable Standing Desk</t>
+          <t>Non-Contact Tonometer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Office Furniture</t>
+          <t>Diagnostic Equipment</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -581,21 +581,221 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ELEC-CABLE-008</t>
+          <t>DIAG-AUTO-008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USB-C Cable 2m (Legacy)</t>
+          <t>Auto Lensmeter</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Diagnostic Equipment</t>
         </is>
       </c>
       <c r="D9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CONS-WIPE-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Lens Cleaning Wipes (Pack of 200)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Clinical Consumables</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CONS-DROP-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Diagnostic Dilation Drops (Box of 50)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Clinical Consumables</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CONS-COVER-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Disposable Chin Rest Covers (Pack of 500)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Clinical Consumables</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CONS-CALSTRIP-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Calibration Test Strips (Box of 100)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Clinical Consumables</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PART-BULB-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Slit Lamp Replacement Bulb</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Service Parts</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PART-CHINREST-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chin Rest Assembly (Replacement)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Service Parts</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PART-CAL-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tonometer Calibration Kit</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Service Parts</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PART-FILTER-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Legacy Filter Module (Discontinued)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Service Parts</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SW-LIC-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Diagnostic Imaging Software License (Annual)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Software &amp; Service Packages</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SW-SVC-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Preventive Maintenance Service Package (Standard)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Software &amp; Service Packages</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
